--- a/docs/product-import-template.xlsx
+++ b/docs/product-import-template.xlsx
@@ -346,10 +346,20 @@
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
+        <t>Image file name WITHOUT the extension — normally just the SKU.
+Name the file after the SKU (BH-001.png) and put it in one folder,
+then import with --images-dir=&lt;folder&gt;.
+Accepted types: .png .jpg .jpeg .webp
+Leave empty to use the SKU automatically; images are only
+imported when --images-dir is passed.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
         <t>Optional country of origin, e.g. Romania.</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <t>Optional extra attributes as JSON, e.g. {"brand":"Balkan House"}
 Must be valid JSON or the import fails for that row.</t>
@@ -648,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -666,8 +676,9 @@
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -748,10 +759,15 @@
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
           <t>country_of_origin</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>attributes</t>
         </is>
@@ -833,10 +849,15 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
+          <t>BH-001</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>{"brand":"Balkan House"}</t>
         </is>
@@ -860,6 +881,7 @@
       <c r="O3" s="5" t="n"/>
       <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -879,6 +901,7 @@
       <c r="O4" s="5" t="n"/>
       <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
@@ -898,6 +921,7 @@
       <c r="O5" s="5" t="n"/>
       <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -917,6 +941,7 @@
       <c r="O6" s="5" t="n"/>
       <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -936,6 +961,7 @@
       <c r="O7" s="5" t="n"/>
       <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -955,6 +981,7 @@
       <c r="O8" s="5" t="n"/>
       <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -974,6 +1001,7 @@
       <c r="O9" s="5" t="n"/>
       <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -993,6 +1021,7 @@
       <c r="O10" s="5" t="n"/>
       <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1012,6 +1041,7 @@
       <c r="O11" s="5" t="n"/>
       <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1031,6 +1061,7 @@
       <c r="O12" s="5" t="n"/>
       <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -1050,6 +1081,7 @@
       <c r="O13" s="5" t="n"/>
       <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1069,6 +1101,7 @@
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1088,6 +1121,7 @@
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1107,6 +1141,7 @@
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1126,6 +1161,7 @@
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1145,6 +1181,7 @@
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -1164,6 +1201,7 @@
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1183,6 +1221,7 @@
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1202,6 +1241,7 @@
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -1221,6 +1261,7 @@
       <c r="O22" s="5" t="n"/>
       <c r="P22" s="5" t="n"/>
       <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1240,6 +1281,7 @@
       <c r="O23" s="5" t="n"/>
       <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1259,6 +1301,7 @@
       <c r="O24" s="5" t="n"/>
       <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -1278,6 +1321,7 @@
       <c r="O25" s="5" t="n"/>
       <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -1297,6 +1341,7 @@
       <c r="O26" s="5" t="n"/>
       <c r="P26" s="5" t="n"/>
       <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1316,6 +1361,7 @@
       <c r="O27" s="5" t="n"/>
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -1335,6 +1381,7 @@
       <c r="O28" s="5" t="n"/>
       <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1354,6 +1401,7 @@
       <c r="O29" s="5" t="n"/>
       <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1373,6 +1421,7 @@
       <c r="O30" s="5" t="n"/>
       <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -1392,6 +1441,7 @@
       <c r="O31" s="5" t="n"/>
       <c r="P31" s="5" t="n"/>
       <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -1411,6 +1461,7 @@
       <c r="O32" s="5" t="n"/>
       <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -1430,6 +1481,7 @@
       <c r="O33" s="5" t="n"/>
       <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -1449,6 +1501,7 @@
       <c r="O34" s="5" t="n"/>
       <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -1468,6 +1521,7 @@
       <c r="O35" s="5" t="n"/>
       <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -1487,6 +1541,7 @@
       <c r="O36" s="5" t="n"/>
       <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="n"/>
+      <c r="R36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -1506,6 +1561,7 @@
       <c r="O37" s="5" t="n"/>
       <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -1525,6 +1581,7 @@
       <c r="O38" s="5" t="n"/>
       <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -1544,6 +1601,7 @@
       <c r="O39" s="5" t="n"/>
       <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="n"/>
+      <c r="R39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -1563,6 +1621,7 @@
       <c r="O40" s="5" t="n"/>
       <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="n"/>
+      <c r="R40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -1582,6 +1641,7 @@
       <c r="O41" s="5" t="n"/>
       <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="n"/>
+      <c r="R41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -1601,6 +1661,7 @@
       <c r="O42" s="5" t="n"/>
       <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="n"/>
+      <c r="R42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -1620,6 +1681,7 @@
       <c r="O43" s="5" t="n"/>
       <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -1639,6 +1701,7 @@
       <c r="O44" s="5" t="n"/>
       <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="n"/>
+      <c r="R44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -1658,6 +1721,7 @@
       <c r="O45" s="5" t="n"/>
       <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="n"/>
+      <c r="R45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -1677,6 +1741,7 @@
       <c r="O46" s="5" t="n"/>
       <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="n"/>
+      <c r="R46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -1696,6 +1761,7 @@
       <c r="O47" s="5" t="n"/>
       <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="n"/>
+      <c r="R47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -1715,6 +1781,7 @@
       <c r="O48" s="5" t="n"/>
       <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -1734,6 +1801,7 @@
       <c r="O49" s="5" t="n"/>
       <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -1753,6 +1821,7 @@
       <c r="O50" s="5" t="n"/>
       <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="n"/>
+      <c r="R50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -1772,6 +1841,7 @@
       <c r="O51" s="5" t="n"/>
       <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="n"/>
+      <c r="R51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -1791,6 +1861,7 @@
       <c r="O52" s="5" t="n"/>
       <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="n"/>
+      <c r="R52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -1810,6 +1881,7 @@
       <c r="O53" s="5" t="n"/>
       <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="n"/>
+      <c r="R53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -1829,6 +1901,7 @@
       <c r="O54" s="5" t="n"/>
       <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="n"/>
+      <c r="R54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -1848,6 +1921,7 @@
       <c r="O55" s="5" t="n"/>
       <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="n"/>
+      <c r="R55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -1867,6 +1941,7 @@
       <c r="O56" s="5" t="n"/>
       <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="n"/>
+      <c r="R56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -1886,6 +1961,7 @@
       <c r="O57" s="5" t="n"/>
       <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -1905,6 +1981,7 @@
       <c r="O58" s="5" t="n"/>
       <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -1924,6 +2001,7 @@
       <c r="O59" s="5" t="n"/>
       <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="n"/>
+      <c r="R59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -1943,6 +2021,7 @@
       <c r="O60" s="5" t="n"/>
       <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="n"/>
+      <c r="R60" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1967,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2397,7 +2476,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>country_of_origin</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
@@ -2407,50 +2486,123 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Optional country of origin, e.g. Romania.</t>
+          <t>Image file name WITHOUT the extension — normally just the SKU. Name the file after the SKU (BH-001.png) and put it in one folder, then import with --images-dir=&lt;folder&gt;. Accepted types: .png .jpg .jpeg .webp Leave empty to use the SKU automatically; images are only imported when --images-dir is passed.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
+          <t>country_of_origin</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Optional country of origin, e.g. Romania.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
           <t>attributes</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>Optional extra attributes as JSON, e.g. {"brand":"Balkan House"} Must be valid JSON or the import fails for that row.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>•  Product images are NOT imported from this file. Upload them in the admin (Catalog → Media) and attach them to the product.</t>
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Images</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>•  Header names are case-insensitive and spaces become underscores, so 'Price DKK' also works as 'price_dkk'.</t>
+          <t>1.  Name every image file after its product SKU: BH-001.png, BH-002.jpg, ...</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>2.  Put them all in one folder (any folder, e.g. product-images/).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>3.  Leave the 'image' column empty to use the SKU automatically, or type a different file name (without extension) to override it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>4.  Import with the folder:</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    pnpm import:products -- &lt;file.xlsx&gt; --images-dir=product-images</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Each image is uploaded to the media library keeping its file name, so it appears there as BH-001.png and is easy to find by SKU. Re-running the import reuses the existing upload instead of creating duplicates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Products that already have an image are left alone; add --replace-images to overwrite them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Accepted file types: .png  .jpg  .jpeg  .webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>•  Header names are case-insensitive and spaces become underscores, so 'Price DKK' also works as 'price_dkk'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>•  Rows are validated before anything is written: if one row is invalid, the import stops and reports the row number.</t>
         </is>

--- a/docs/product-import-template.xlsx
+++ b/docs/product-import-template.xlsx
@@ -359,12 +359,6 @@
         <t>Optional country of origin, e.g. Romania.</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional extra attributes as JSON, e.g. {"brand":"Balkan House"}
-Must be valid JSON or the import fails for that row.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -658,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -678,7 +672,6 @@
     <col width="34" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -767,11 +760,6 @@
           <t>country_of_origin</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>attributes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -855,11 +843,6 @@
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Romania</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>{"brand":"Balkan House"}</t>
         </is>
       </c>
     </row>
@@ -881,7 +864,6 @@
       <c r="O3" s="5" t="n"/>
       <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="n"/>
-      <c r="R3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -901,7 +883,6 @@
       <c r="O4" s="5" t="n"/>
       <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="n"/>
-      <c r="R4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
@@ -921,7 +902,6 @@
       <c r="O5" s="5" t="n"/>
       <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -941,7 +921,6 @@
       <c r="O6" s="5" t="n"/>
       <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -961,7 +940,6 @@
       <c r="O7" s="5" t="n"/>
       <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -981,7 +959,6 @@
       <c r="O8" s="5" t="n"/>
       <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -1001,7 +978,6 @@
       <c r="O9" s="5" t="n"/>
       <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -1021,7 +997,6 @@
       <c r="O10" s="5" t="n"/>
       <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1041,7 +1016,6 @@
       <c r="O11" s="5" t="n"/>
       <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1061,7 +1035,6 @@
       <c r="O12" s="5" t="n"/>
       <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -1081,7 +1054,6 @@
       <c r="O13" s="5" t="n"/>
       <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1101,7 +1073,6 @@
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1121,7 +1092,6 @@
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1141,7 +1111,6 @@
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -1161,7 +1130,6 @@
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
       <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -1181,7 +1149,6 @@
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -1201,7 +1168,6 @@
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1221,7 +1187,6 @@
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1241,7 +1206,6 @@
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -1261,7 +1225,6 @@
       <c r="O22" s="5" t="n"/>
       <c r="P22" s="5" t="n"/>
       <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1281,7 +1244,6 @@
       <c r="O23" s="5" t="n"/>
       <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -1301,7 +1263,6 @@
       <c r="O24" s="5" t="n"/>
       <c r="P24" s="5" t="n"/>
       <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -1321,7 +1282,6 @@
       <c r="O25" s="5" t="n"/>
       <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -1341,7 +1301,6 @@
       <c r="O26" s="5" t="n"/>
       <c r="P26" s="5" t="n"/>
       <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1361,7 +1320,6 @@
       <c r="O27" s="5" t="n"/>
       <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -1381,7 +1339,6 @@
       <c r="O28" s="5" t="n"/>
       <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1401,7 +1358,6 @@
       <c r="O29" s="5" t="n"/>
       <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="n"/>
-      <c r="R29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1421,7 +1377,6 @@
       <c r="O30" s="5" t="n"/>
       <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -1441,7 +1396,6 @@
       <c r="O31" s="5" t="n"/>
       <c r="P31" s="5" t="n"/>
       <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -1461,7 +1415,6 @@
       <c r="O32" s="5" t="n"/>
       <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -1481,7 +1434,6 @@
       <c r="O33" s="5" t="n"/>
       <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -1501,7 +1453,6 @@
       <c r="O34" s="5" t="n"/>
       <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="n"/>
-      <c r="R34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -1521,7 +1472,6 @@
       <c r="O35" s="5" t="n"/>
       <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="n"/>
-      <c r="R35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -1541,7 +1491,6 @@
       <c r="O36" s="5" t="n"/>
       <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="n"/>
-      <c r="R36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -1561,7 +1510,6 @@
       <c r="O37" s="5" t="n"/>
       <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="n"/>
-      <c r="R37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -1581,7 +1529,6 @@
       <c r="O38" s="5" t="n"/>
       <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="n"/>
-      <c r="R38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -1601,7 +1548,6 @@
       <c r="O39" s="5" t="n"/>
       <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="n"/>
-      <c r="R39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -1621,7 +1567,6 @@
       <c r="O40" s="5" t="n"/>
       <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="n"/>
-      <c r="R40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -1641,7 +1586,6 @@
       <c r="O41" s="5" t="n"/>
       <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="n"/>
-      <c r="R41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -1661,7 +1605,6 @@
       <c r="O42" s="5" t="n"/>
       <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="n"/>
-      <c r="R42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -1681,7 +1624,6 @@
       <c r="O43" s="5" t="n"/>
       <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5" t="n"/>
-      <c r="R43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -1701,7 +1643,6 @@
       <c r="O44" s="5" t="n"/>
       <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="n"/>
-      <c r="R44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -1721,7 +1662,6 @@
       <c r="O45" s="5" t="n"/>
       <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="n"/>
-      <c r="R45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -1741,7 +1681,6 @@
       <c r="O46" s="5" t="n"/>
       <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="n"/>
-      <c r="R46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -1761,7 +1700,6 @@
       <c r="O47" s="5" t="n"/>
       <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="n"/>
-      <c r="R47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -1781,7 +1719,6 @@
       <c r="O48" s="5" t="n"/>
       <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -1801,7 +1738,6 @@
       <c r="O49" s="5" t="n"/>
       <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="n"/>
-      <c r="R49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -1821,7 +1757,6 @@
       <c r="O50" s="5" t="n"/>
       <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="n"/>
-      <c r="R50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -1841,7 +1776,6 @@
       <c r="O51" s="5" t="n"/>
       <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="n"/>
-      <c r="R51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -1861,7 +1795,6 @@
       <c r="O52" s="5" t="n"/>
       <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="n"/>
-      <c r="R52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -1881,7 +1814,6 @@
       <c r="O53" s="5" t="n"/>
       <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="n"/>
-      <c r="R53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -1901,7 +1833,6 @@
       <c r="O54" s="5" t="n"/>
       <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="n"/>
-      <c r="R54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -1921,7 +1852,6 @@
       <c r="O55" s="5" t="n"/>
       <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="n"/>
-      <c r="R55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -1941,7 +1871,6 @@
       <c r="O56" s="5" t="n"/>
       <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="n"/>
-      <c r="R56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -1961,7 +1890,6 @@
       <c r="O57" s="5" t="n"/>
       <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -1981,7 +1909,6 @@
       <c r="O58" s="5" t="n"/>
       <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -2001,7 +1928,6 @@
       <c r="O59" s="5" t="n"/>
       <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="n"/>
-      <c r="R59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -2021,7 +1947,6 @@
       <c r="O60" s="5" t="n"/>
       <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="n"/>
-      <c r="R60" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2046,7 +1971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2507,102 +2432,85 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>attributes</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>Optional extra attributes as JSON, e.g. {"brand":"Balkan House"} Must be valid JSON or the import fails for that row.</t>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Images</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>Images</t>
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>1.  Name every image file after its product SKU: BH-001.png, BH-002.jpg, ...</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>1.  Name every image file after its product SKU: BH-001.png, BH-002.jpg, ...</t>
+          <t>2.  Put them all in one folder (any folder, e.g. product-images/).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>2.  Put them all in one folder (any folder, e.g. product-images/).</t>
+          <t>3.  Leave the 'image' column empty to use the SKU automatically, or type a different file name (without extension) to override it.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>3.  Leave the 'image' column empty to use the SKU automatically, or type a different file name (without extension) to override it.</t>
+          <t>4.  Import with the folder:</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>4.  Import with the folder:</t>
+          <t xml:space="preserve">    pnpm import:products -- &lt;file.xlsx&gt; --images-dir=product-images</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    pnpm import:products -- &lt;file.xlsx&gt; --images-dir=product-images</t>
+          <t>Each image is uploaded to the media library keeping its file name, so it appears there as BH-001.png and is easy to find by SKU. Re-running the import reuses the existing upload instead of creating duplicates.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Each image is uploaded to the media library keeping its file name, so it appears there as BH-001.png and is easy to find by SKU. Re-running the import reuses the existing upload instead of creating duplicates.</t>
+          <t>Products that already have an image are left alone; add --replace-images to overwrite them.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>Products that already have an image are left alone; add --replace-images to overwrite them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
           <t>Accepted file types: .png  .jpg  .jpeg  .webp</t>
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>•  Header names are case-insensitive and spaces become underscores, so 'Price DKK' also works as 'price_dkk'.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>•  Header names are case-insensitive and spaces become underscores, so 'Price DKK' also works as 'price_dkk'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>•  Rows are validated before anything is written: if one row is invalid, the import stops and reports the row number.</t>
         </is>

--- a/docs/product-import-template.xlsx
+++ b/docs/product-import-template.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tdch1026685-my.sharepoint.com/personal/vam_apportsystems_com/Documents/Documents/GitHub/balkanhouse/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_EA1451EC32E38E4D58C7798418F31DD4D57AEA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC634EF7-F9E9-45E9-AEC5-37FED3E322ED}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_EA1451EC32E38E4D58C7798418F31DD4D57AEA5E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFDEBD05-B1FE-4506-9615-4BE6E3A8A4EB}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="3140" windowWidth="34970" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="3140" windowWidth="34970" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
-    <sheet name="Reference" sheetId="3" r:id="rId3"/>
+    <sheet name="Reference" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -289,7 +288,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
   <si>
     <t>sku</t>
   </si>
@@ -391,174 +390,6 @@
   </si>
   <si>
     <t>Romania</t>
-  </si>
-  <si>
-    <t>Balkan House — product import template</t>
-  </si>
-  <si>
-    <t>Fill in the 'Products' sheet, then import it with the command below. One row = one product.</t>
-  </si>
-  <si>
-    <t>Before you import</t>
-  </si>
-  <si>
-    <t>1.  DELETE the yellow example row (row 2) in the 'Products' sheet — otherwise it is imported as a real product.</t>
-  </si>
-  <si>
-    <t>2.  Keep the header row exactly as it is. Column names must not be renamed, translated or reordered... reordering is fine, renaming is not.</t>
-  </si>
-  <si>
-    <t>3.  Categories must already exist in the admin before import (see the Reference sheet for the current list).</t>
-  </si>
-  <si>
-    <t>4.  Save as .xlsx (recommended). CSV also works, but a comma inside any value — such as the allergens list — will corrupt a CSV.</t>
-  </si>
-  <si>
-    <t>How to import</t>
-  </si>
-  <si>
-    <t>Always dry-run first — it validates every row and writes nothing:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    pnpm import:products -- docs/product-import-template.xlsx --dry-run</t>
-  </si>
-  <si>
-    <t>Then run the real import:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    pnpm import:products -- docs/product-import-template.xlsx</t>
-  </si>
-  <si>
-    <t>Products are matched by 'sku': an existing SKU is UPDATED, a new SKU is CREATED. Nothing is ever deleted.</t>
-  </si>
-  <si>
-    <t>Languages</t>
-  </si>
-  <si>
-    <t>Three fields can be translated: title, ingredients and description. Each has one column per language:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    title_ro / title_da / title_en          (Romanian / Danish / English)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ingredients_ro / ingredients_da / ingredients_en</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    description_ro / description_da / description_en</t>
-  </si>
-  <si>
-    <t>Romanian is the default language. If a Danish or English value is left empty, the shop shows the Romanian text on that language's pages, so you can add translations later without breaking anything.</t>
-  </si>
-  <si>
-    <t>Do NOT add plain 'title', 'ingredients' or 'description' columns: the importer treats them as Romanian and they would silently override your *_ro columns.</t>
-  </si>
-  <si>
-    <t>Columns</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Required</t>
-  </si>
-  <si>
-    <t>What to put in it</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Unique product code. Used to match existing products: an existing SKU is updated, a new one is created. Also becomes part of the product URL.</t>
-  </si>
-  <si>
-    <t>Romanian product name. If left empty for a NEW product, the SKU is used as the name.</t>
-  </si>
-  <si>
-    <t>optional</t>
-  </si>
-  <si>
-    <t>Danish product name. Optional. If empty, the shop falls back to the Romanian title on /da/.</t>
-  </si>
-  <si>
-    <t>English product name. Optional. If empty, the shop falls back to the Romanian title on /en/.</t>
-  </si>
-  <si>
-    <t>Price in Danish kroner, VAT included. Use a number (e.g. 49.95). Do not type 'kr.' or currency symbols.</t>
-  </si>
-  <si>
-    <t>Selling unit: piece or kg. Also accepted: buc, bucata, kilogram. Defaults to 'piece' if left empty.</t>
-  </si>
-  <si>
-    <t>Stock indicator: in, low or out. Romanian labels also accepted: în stoc, stoc redus, epuizat. Defaults to 'in' if left empty.</t>
-  </si>
-  <si>
-    <t>Category slug (see the Reference sheet). The category MUST already exist in the admin before importing. Leave empty for no category.</t>
-  </si>
-  <si>
-    <t>Comma-separated EU allergen codes, e.g. gluten,milk,nuts Valid codes are listed on the Reference sheet. Leave empty if none.</t>
-  </si>
-  <si>
-    <t>Romanian ingredient list. Optional.</t>
-  </si>
-  <si>
-    <t>Danish ingredient list. Optional.</t>
-  </si>
-  <si>
-    <t>English ingredient list. Optional.</t>
-  </si>
-  <si>
-    <t>Romanian description (plain text; converted to rich text on import).</t>
-  </si>
-  <si>
-    <t>Danish description (plain text). Optional.</t>
-  </si>
-  <si>
-    <t>English description (plain text). Optional.</t>
-  </si>
-  <si>
-    <t>Image file name WITHOUT the extension — normally just the SKU. Name the file after the SKU (BH-001.png) and put it in one folder, then import with --images-dir=&lt;folder&gt;. Accepted types: .png .jpg .jpeg .webp Leave empty to use the SKU automatically; images are only imported when --images-dir is passed.</t>
-  </si>
-  <si>
-    <t>Shared related-products keyword (e.g. bread). Products with the same keyword appear as related on the product page. Stored lowercase.</t>
-  </si>
-  <si>
-    <t>Optional country of origin, e.g. Romania.</t>
-  </si>
-  <si>
-    <t>Images</t>
-  </si>
-  <si>
-    <t>1.  Name every image file after its product SKU: BH-001.png, BH-002.jpg, ...</t>
-  </si>
-  <si>
-    <t>2.  Put them all in one folder (any folder, e.g. product-images/).</t>
-  </si>
-  <si>
-    <t>3.  Leave the 'image' column empty to use the SKU automatically, or type a different file name (without extension) to override it.</t>
-  </si>
-  <si>
-    <t>4.  Import with the folder:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    pnpm import:products -- &lt;file.xlsx&gt; --images-dir=product-images</t>
-  </si>
-  <si>
-    <t>Each image is uploaded to the media library keeping its file name, so it appears there as BH-001.png and is easy to find by SKU. Re-running the import reuses the existing upload instead of creating duplicates.</t>
-  </si>
-  <si>
-    <t>Products that already have an image are left alone; add --replace-images to overwrite them.</t>
-  </si>
-  <si>
-    <t>Accepted file types: .png  .jpg  .jpeg  .webp</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>•  Header names are case-insensitive and spaces become underscores, so 'Price DKK' also works as 'price_dkk'.</t>
-  </si>
-  <si>
-    <t>•  Rows are validated before anything is written: if one row is invalid, the import stops and reports the row number.</t>
   </si>
   <si>
     <t>Categories (category_slug)</t>
@@ -694,7 +525,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -720,36 +551,8 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FF6B1D2A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF2C1810"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color rgb="FF6B1D2A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF2C1810"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF9B2335"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -809,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -830,25 +633,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2462,395 +2249,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C58"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="78" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="50" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="65" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="75" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="50" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="62.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="50" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="50" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="78" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A27" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A33" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A34" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A35" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="50" x14ac:dyDescent="0.35">
-      <c r="A42" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="25" x14ac:dyDescent="0.35">
-      <c r="A43" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="62.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="50" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="25" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="50" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" ht="50" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2861,217 +2259,217 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>90</v>
+      <c r="A1" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>92</v>
+      <c r="A2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>94</v>
+      <c r="A3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>95</v>
+      <c r="B4" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>97</v>
+      <c r="A5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>99</v>
+      <c r="A6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>101</v>
+      <c r="A7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
-        <v>102</v>
+      <c r="A9" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>103</v>
+      <c r="A11" s="7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>105</v>
+      <c r="A12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>106</v>
+      <c r="B13" s="9" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>108</v>
+      <c r="A14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
-        <v>109</v>
+      <c r="A16" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>110</v>
+      <c r="A18" s="7" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>105</v>
+      <c r="A19" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>111</v>
+      <c r="B20" s="9" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>113</v>
+      <c r="A21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>115</v>
+      <c r="A22" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="18" t="s">
-        <v>116</v>
+      <c r="A24" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="9" t="s">
-        <v>117</v>
+      <c r="A26" s="7" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="12" t="s">
-        <v>118</v>
+      <c r="A27" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="17" t="s">
-        <v>119</v>
+      <c r="A28" s="9" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="17" t="s">
-        <v>120</v>
+      <c r="A29" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="17" t="s">
-        <v>121</v>
+      <c r="A30" s="9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="17" t="s">
-        <v>122</v>
+      <c r="A31" s="9" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="17" t="s">
-        <v>123</v>
+      <c r="A32" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="17" t="s">
-        <v>124</v>
+      <c r="A33" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="17" t="s">
-        <v>125</v>
+      <c r="A34" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" s="17" t="s">
-        <v>126</v>
+      <c r="A35" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A36" s="17" t="s">
-        <v>127</v>
+      <c r="A36" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A37" s="17" t="s">
-        <v>128</v>
+      <c r="A37" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A38" s="17" t="s">
-        <v>129</v>
+      <c r="A38" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A39" s="17" t="s">
-        <v>130</v>
+      <c r="A39" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A40" s="17" t="s">
-        <v>131</v>
+      <c r="A40" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A41" s="17" t="s">
-        <v>132</v>
+      <c r="A41" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
